--- a/04_3일차_팀프로젝트_실습기획서.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\나의_SSAFY_이야기\AI_온보딩_[팀_프로젝트]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB82290-5A8F-4D03-B765-220BF681ABAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EEFC68-31EA-436C-85C6-6CB043DFA867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8895" yWindow="2250" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="2145" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="279">
   <si>
     <t>실습 소재</t>
   </si>
@@ -8778,6 +8778,9 @@
   </si>
   <si>
     <t>PPT·시연 리허설 및 SSAFY GitLab 최종 제출</t>
+  </si>
+  <si>
+    <t>jovial-phoenix-52d898.netlify.app</t>
   </si>
 </sst>
 </file>
@@ -8785,9 +8788,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="m/d"/>
+    <numFmt numFmtId="176" formatCode="m/d"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9114,6 +9117,14 @@
       <color rgb="FF222222"/>
       <name val="Noto Sans CJK SC"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -9288,10 +9299,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -9397,6 +9409,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9538,44 +9562,13 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0C8798"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0C8798"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0C8798"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -9862,10 +9855,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="45"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -9900,10 +9893,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="46"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -9954,28 +9947,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="44"/>
+      <c r="C17" s="48"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="47"/>
+      <c r="C18" s="51"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="40"/>
+      <c r="C19" s="44"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="40"/>
+      <c r="C20" s="44"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -10009,13 +10002,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -10107,46 +10100,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10179,22 +10172,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="42"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -10243,16 +10236,16 @@
       <c r="B7" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="88" t="s">
+      <c r="E7" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="88" t="s">
+      <c r="F7" s="39" t="s">
         <v>181</v>
       </c>
     </row>
@@ -10260,16 +10253,16 @@
       <c r="B8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="E8" s="88" t="s">
+      <c r="E8" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="39" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10277,16 +10270,16 @@
       <c r="B9" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="88" t="s">
+      <c r="D9" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="88" t="s">
+      <c r="E9" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="F9" s="88" t="s">
+      <c r="F9" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10294,16 +10287,16 @@
       <c r="B10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="88" t="s">
+      <c r="D10" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="E10" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="F10" s="88" t="s">
+      <c r="F10" s="39" t="s">
         <v>191</v>
       </c>
     </row>
@@ -10311,16 +10304,16 @@
       <c r="B11" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="E11" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="F11" s="88" t="s">
+      <c r="F11" s="39" t="s">
         <v>195</v>
       </c>
     </row>
@@ -10328,16 +10321,16 @@
       <c r="B12" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="E12" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="88" t="s">
+      <c r="F12" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10345,16 +10338,16 @@
       <c r="B13" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="88" t="s">
+      <c r="F13" s="39" t="s">
         <v>200</v>
       </c>
     </row>
@@ -10362,16 +10355,16 @@
       <c r="B14" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="E14" s="88" t="s">
+      <c r="E14" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="39" t="s">
         <v>204</v>
       </c>
     </row>
@@ -10379,16 +10372,16 @@
       <c r="B15" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="88" t="s">
+      <c r="D15" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="88" t="s">
+      <c r="E15" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="88" t="s">
+      <c r="F15" s="39" t="s">
         <v>209</v>
       </c>
     </row>
@@ -10396,16 +10389,16 @@
       <c r="B16" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="E16" s="88" t="s">
+      <c r="E16" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10413,16 +10406,16 @@
       <c r="B17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="88" t="s">
+      <c r="F17" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10430,16 +10423,16 @@
       <c r="B18" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="88" t="s">
+      <c r="D18" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="E18" s="88" t="s">
+      <c r="E18" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="F18" s="88" t="s">
+      <c r="F18" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10447,16 +10440,16 @@
       <c r="B19" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="D19" s="88" t="s">
+      <c r="D19" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="88" t="s">
+      <c r="E19" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="88" t="s">
+      <c r="F19" s="39" t="s">
         <v>220</v>
       </c>
     </row>
@@ -10464,16 +10457,16 @@
       <c r="B20" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C20" s="88" t="s">
+      <c r="C20" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="D20" s="88" t="s">
+      <c r="D20" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="E20" s="88" t="s">
+      <c r="E20" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="F20" s="88" t="s">
+      <c r="F20" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10481,16 +10474,16 @@
       <c r="B21" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="D21" s="88" t="s">
+      <c r="D21" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="E21" s="88" t="s">
+      <c r="E21" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="F21" s="88" t="s">
+      <c r="F21" s="39" t="s">
         <v>188</v>
       </c>
     </row>
@@ -10498,16 +10491,16 @@
       <c r="B22" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="D22" s="88" t="s">
+      <c r="D22" s="39" t="s">
         <v>226</v>
       </c>
-      <c r="E22" s="88" t="s">
+      <c r="E22" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="F22" s="88" t="s">
+      <c r="F22" s="39" t="s">
         <v>228</v>
       </c>
     </row>
@@ -10515,16 +10508,16 @@
       <c r="B23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="D23" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="E23" s="88" t="s">
+      <c r="E23" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="F23" s="88" t="s">
+      <c r="F23" s="39" t="s">
         <v>232</v>
       </c>
     </row>
@@ -10532,16 +10525,16 @@
       <c r="B24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="E24" s="88" t="s">
+      <c r="E24" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="F24" s="88" t="s">
+      <c r="F24" s="39" t="s">
         <v>236</v>
       </c>
     </row>
@@ -10728,37 +10721,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="42"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="46"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="42"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="46"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -10784,7 +10777,7 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="40" t="s">
         <v>237</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -10808,7 +10801,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" s="27" customFormat="1" ht="25.5">
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="40" t="s">
         <v>239</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -10832,7 +10825,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="40" t="s">
         <v>241</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -10856,10 +10849,10 @@
       </c>
     </row>
     <row r="9" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="39" t="s">
         <v>244</v>
       </c>
       <c r="D9" s="5">
@@ -10880,10 +10873,10 @@
       </c>
     </row>
     <row r="10" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="39" t="s">
         <v>221</v>
       </c>
       <c r="D10" s="5">
@@ -10904,7 +10897,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B11" s="89" t="s">
+      <c r="B11" s="40" t="s">
         <v>245</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -10928,7 +10921,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="40" t="s">
         <v>158</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -10952,10 +10945,10 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="39" t="s">
         <v>248</v>
       </c>
       <c r="D13" s="5">
@@ -11045,14 +11038,14 @@
       <c r="B21" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="61" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="44"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11063,7 +11056,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="G6:G19">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11101,16 +11094,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="51"/>
+      <c r="C2" s="55"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="46"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -11145,133 +11138,133 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="66"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="51"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="C11" s="47"/>
+      <c r="C11" s="51"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="50" t="s">
         <v>251</v>
       </c>
-      <c r="C12" s="47"/>
+      <c r="C12" s="51"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="50" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="47"/>
+      <c r="C13" s="51"/>
     </row>
     <row r="14" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="47"/>
+      <c r="C14" s="51"/>
     </row>
     <row r="15" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B15" s="59"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="51"/>
     </row>
     <row r="16" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B16" s="46"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="51"/>
     </row>
     <row r="17" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="47"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
     </row>
     <row r="18" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B18" s="59"/>
-      <c r="C18" s="47"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="51"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="67"/>
+      <c r="C20" s="71"/>
     </row>
     <row r="21" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="47"/>
+      <c r="C21" s="51"/>
     </row>
     <row r="22" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="C22" s="47"/>
+      <c r="C22" s="51"/>
     </row>
     <row r="23" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="50" t="s">
         <v>256</v>
       </c>
-      <c r="C23" s="47"/>
+      <c r="C23" s="51"/>
     </row>
     <row r="24" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B24" s="59"/>
-      <c r="C24" s="47"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="51"/>
     </row>
     <row r="25" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B25" s="59"/>
-      <c r="C25" s="60"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="64"/>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B26" s="59"/>
-      <c r="C26" s="47"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="51"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1">
-      <c r="B28" s="64" t="s">
+      <c r="B28" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="65"/>
+      <c r="C28" s="69"/>
     </row>
     <row r="29" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="50" t="s">
         <v>257</v>
       </c>
-      <c r="C29" s="47"/>
+      <c r="C29" s="51"/>
     </row>
     <row r="30" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="C30" s="47"/>
+      <c r="C30" s="51"/>
     </row>
     <row r="31" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="50" t="s">
         <v>259</v>
       </c>
-      <c r="C31" s="47"/>
+      <c r="C31" s="51"/>
     </row>
     <row r="32" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B32" s="59"/>
-      <c r="C32" s="60"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="64"/>
     </row>
     <row r="33" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="59"/>
-      <c r="C33" s="60"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="64"/>
     </row>
     <row r="34" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B34" s="59"/>
-      <c r="C34" s="60"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="64"/>
     </row>
     <row r="35" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B35" s="59"/>
-      <c r="C35" s="47"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -11314,7 +11307,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:M28"/>
+  <dimension ref="B2:Q28"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -11330,39 +11323,42 @@
     <col min="12" max="12" width="7.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="81" t="s">
+    <row r="2" spans="2:17" ht="27.75" customHeight="1">
+      <c r="B2" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-    </row>
-    <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="80" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+    </row>
+    <row r="3" spans="2:17" ht="79.7" customHeight="1">
+      <c r="B3" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="42"/>
-    </row>
-    <row r="4" spans="2:13" ht="25.5" customHeight="1">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="46"/>
+      <c r="Q3" s="92" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="25.5" customHeight="1">
       <c r="B4" s="13" t="s">
         <v>52</v>
       </c>
@@ -11390,33 +11386,33 @@
       <c r="J4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="91">
+      <c r="K4" s="42">
         <v>46217</v>
       </c>
-      <c r="L4" s="91">
+      <c r="L4" s="42">
         <v>46218</v>
       </c>
-      <c r="M4" s="91">
+      <c r="M4" s="42">
         <v>46219</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="30" customHeight="1">
+    <row r="5" spans="2:17" ht="30" customHeight="1">
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="D5" s="39" t="s">
         <v>260</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="90">
+      <c r="F5" s="41">
         <v>46217</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="41">
         <v>46217</v>
       </c>
       <c r="H5" s="5">
@@ -11433,23 +11429,23 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="2:13" ht="30" customHeight="1">
+    <row r="6" spans="2:17" ht="30" customHeight="1">
       <c r="B6" s="5">
         <v>2</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="39" t="s">
         <v>261</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="41">
         <v>46217</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="41">
         <v>46217</v>
       </c>
       <c r="H6" s="5">
@@ -11466,23 +11462,23 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="2:13" ht="30" customHeight="1">
+    <row r="7" spans="2:17" ht="30" customHeight="1">
       <c r="B7" s="5">
         <v>3</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="39" t="s">
         <v>263</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="41">
         <v>46217</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="41">
         <v>46217</v>
       </c>
       <c r="H7" s="5">
@@ -11499,23 +11495,23 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="2:13" ht="30" customHeight="1">
+    <row r="8" spans="2:17" ht="30" customHeight="1">
       <c r="B8" s="5">
         <v>4</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="39" t="s">
         <v>265</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="F8" s="90">
+      <c r="F8" s="41">
         <v>46217</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="41">
         <v>46219</v>
       </c>
       <c r="H8" s="5">
@@ -11532,23 +11528,23 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="2:13" ht="30" customHeight="1">
+    <row r="9" spans="2:17" ht="30" customHeight="1">
       <c r="B9" s="5">
         <v>5</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="88" t="s">
+      <c r="D9" s="39" t="s">
         <v>267</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="90">
+      <c r="F9" s="41">
         <v>46217</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="41">
         <v>46218</v>
       </c>
       <c r="H9" s="5">
@@ -11565,23 +11561,23 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="2:13" ht="30" customHeight="1">
+    <row r="10" spans="2:17" ht="30" customHeight="1">
       <c r="B10" s="5">
         <v>6</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="88" t="s">
+      <c r="D10" s="39" t="s">
         <v>268</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="90">
+      <c r="F10" s="41">
         <v>46218</v>
       </c>
-      <c r="G10" s="90">
+      <c r="G10" s="41">
         <v>46218</v>
       </c>
       <c r="H10" s="5">
@@ -11598,23 +11594,23 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="2:13" ht="30" customHeight="1">
+    <row r="11" spans="2:17" ht="30" customHeight="1">
       <c r="B11" s="5">
         <v>7</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="39" t="s">
         <v>269</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="41">
         <v>46218</v>
       </c>
-      <c r="G11" s="90">
+      <c r="G11" s="41">
         <v>46218</v>
       </c>
       <c r="H11" s="5">
@@ -11631,23 +11627,23 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="2:13" ht="30" customHeight="1">
+    <row r="12" spans="2:17" ht="30" customHeight="1">
       <c r="B12" s="5">
         <v>8</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="39" t="s">
         <v>270</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="41">
         <v>46218</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="41">
         <v>46218</v>
       </c>
       <c r="H12" s="5">
@@ -11664,23 +11660,23 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="2:13" ht="30" customHeight="1">
+    <row r="13" spans="2:17" ht="30" customHeight="1">
       <c r="B13" s="5">
         <v>9</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="39" t="s">
         <v>271</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="41">
         <v>46218</v>
       </c>
-      <c r="G13" s="90">
+      <c r="G13" s="41">
         <v>46218</v>
       </c>
       <c r="H13" s="5">
@@ -11697,23 +11693,23 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="2:13" ht="30" customHeight="1">
+    <row r="14" spans="2:17" ht="30" customHeight="1">
       <c r="B14" s="5">
         <v>10</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="39" t="s">
         <v>272</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="41">
         <v>46218</v>
       </c>
-      <c r="G14" s="90">
+      <c r="G14" s="41">
         <v>46219</v>
       </c>
       <c r="H14" s="5">
@@ -11721,7 +11717,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>177</v>
@@ -11730,23 +11726,23 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="2:13" ht="30" customHeight="1">
+    <row r="15" spans="2:17" ht="30" customHeight="1">
       <c r="B15" s="5">
         <v>11</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="88" t="s">
+      <c r="D15" s="39" t="s">
         <v>273</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="90">
+      <c r="F15" s="41">
         <v>46219</v>
       </c>
-      <c r="G15" s="90">
+      <c r="G15" s="41">
         <v>46219</v>
       </c>
       <c r="H15" s="5">
@@ -11754,7 +11750,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>274</v>
@@ -11763,23 +11759,23 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="2:13" ht="30" customHeight="1">
+    <row r="16" spans="2:17" ht="30" customHeight="1">
       <c r="B16" s="5">
         <v>12</v>
       </c>
       <c r="C16" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="39" t="s">
         <v>275</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="41">
         <v>46219</v>
       </c>
-      <c r="G16" s="90">
+      <c r="G16" s="41">
         <v>46219</v>
       </c>
       <c r="H16" s="5">
@@ -11787,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>177</v>
@@ -11803,16 +11799,16 @@
       <c r="C17" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="39" t="s">
         <v>276</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="41">
         <v>46219</v>
       </c>
-      <c r="G17" s="90">
+      <c r="G17" s="41">
         <v>46219</v>
       </c>
       <c r="H17" s="5">
@@ -11820,7 +11816,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="5">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>177</v>
@@ -11836,16 +11832,16 @@
       <c r="C18" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="88" t="s">
+      <c r="D18" s="39" t="s">
         <v>277</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="41">
         <v>46219</v>
       </c>
-      <c r="G18" s="90">
+      <c r="G18" s="41">
         <v>46219</v>
       </c>
       <c r="H18" s="5">
@@ -11866,58 +11862,58 @@
       <c r="D19" s="27"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="83"/>
+      <c r="C20" s="87"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="85"/>
+      <c r="C21" s="89"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="87"/>
+      <c r="C22" s="91"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="75"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="73"/>
+      <c r="C24" s="77"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="75"/>
+      <c r="C25" s="79"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="77"/>
+      <c r="C26" s="81"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="79"/>
+      <c r="C27" s="83"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="69"/>
+      <c r="C28" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -11935,7 +11931,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11944,6 +11940,9 @@
       <formula1>"완료,진행중,확인필요,대기"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="Q3" r:id="rId1" display="https://jovial-phoenix-52d898.netlify.app/" xr:uid="{D71CFC42-3DCE-49F3-A017-90875B607020}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -11963,16 +11962,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="51"/>
+      <c r="C2" s="55"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="46"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">

--- a/04_3일차_팀프로젝트_실습기획서.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\나의_SSAFY_이야기\AI_온보딩_[팀_프로젝트]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EEFC68-31EA-436C-85C6-6CB043DFA867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5E1CE8-B6B2-484E-823E-7A1EEF321666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="2145" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="277">
   <si>
     <t>실습 소재</t>
   </si>
@@ -8477,9 +8477,6 @@
     <t>완료</t>
   </si>
   <si>
-    <t>진행중</t>
-  </si>
-  <si>
     <t>선정 권역 제공 JSON 활용</t>
   </si>
   <si>
@@ -8766,9 +8763,6 @@
   </si>
   <si>
     <t>RFP 변경사항·AI 도구 정책 승인 확인</t>
-  </si>
-  <si>
-    <t>확인필요</t>
   </si>
   <si>
     <t>Netlify 배포 및 외부 접속 URL 확인</t>
@@ -9423,6 +9417,7 @@
     <xf numFmtId="176" fontId="35" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9475,12 +9470,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -9488,6 +9477,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9501,6 +9496,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9538,31 +9557,6 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -9855,10 +9849,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="49"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -9893,10 +9887,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="46"/>
+      <c r="C9" s="47"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -9947,28 +9941,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="48"/>
+      <c r="C17" s="49"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="51"/>
+      <c r="C18" s="52"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="44"/>
+      <c r="C19" s="45"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="45"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -10002,13 +9996,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -10100,46 +10094,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="47"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10172,22 +10166,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="46"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="47"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -10237,16 +10231,16 @@
         <v>152</v>
       </c>
       <c r="C7" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="E7" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="F7" s="39" t="s">
         <v>180</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
@@ -10254,16 +10248,16 @@
         <v>152</v>
       </c>
       <c r="C8" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="E8" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="F8" s="39" t="s">
         <v>184</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1">
@@ -10274,13 +10268,13 @@
         <v>172</v>
       </c>
       <c r="D9" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="F9" s="39" t="s">
         <v>187</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
@@ -10288,16 +10282,16 @@
         <v>152</v>
       </c>
       <c r="C10" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="E10" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F10" s="39" t="s">
         <v>190</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
@@ -10305,16 +10299,16 @@
         <v>152</v>
       </c>
       <c r="C11" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="E11" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="F11" s="39" t="s">
         <v>194</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
@@ -10325,13 +10319,13 @@
         <v>154</v>
       </c>
       <c r="D12" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>197</v>
-      </c>
       <c r="F12" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
@@ -10342,13 +10336,13 @@
         <v>155</v>
       </c>
       <c r="D13" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E13" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="F13" s="39" t="s">
         <v>199</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
@@ -10356,33 +10350,33 @@
         <v>152</v>
       </c>
       <c r="C14" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="E14" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="F14" s="39" t="s">
         <v>203</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
       <c r="B15" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="D15" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="E15" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="F15" s="39" t="s">
         <v>208</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
@@ -10390,16 +10384,16 @@
         <v>156</v>
       </c>
       <c r="C16" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>210</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>211</v>
       </c>
       <c r="E16" s="39" t="s">
         <v>157</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
@@ -10410,13 +10404,13 @@
         <v>153</v>
       </c>
       <c r="D17" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="39" t="s">
-        <v>213</v>
-      </c>
       <c r="F17" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
@@ -10424,16 +10418,16 @@
         <v>156</v>
       </c>
       <c r="C18" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="E18" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="E18" s="39" t="s">
-        <v>216</v>
-      </c>
       <c r="F18" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
@@ -10441,16 +10435,16 @@
         <v>156</v>
       </c>
       <c r="C19" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="E19" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="F19" s="39" t="s">
         <v>219</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
@@ -10461,13 +10455,13 @@
         <v>171</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
@@ -10475,16 +10469,16 @@
         <v>159</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="E21" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="E21" s="39" t="s">
-        <v>224</v>
-      </c>
       <c r="F21" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
@@ -10492,16 +10486,16 @@
         <v>159</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="E22" s="39" t="s">
         <v>226</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="F22" s="39" t="s">
         <v>227</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="33" customHeight="1">
@@ -10509,16 +10503,16 @@
         <v>161</v>
       </c>
       <c r="C23" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="E23" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="F23" s="39" t="s">
         <v>231</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="25.5">
@@ -10526,16 +10520,16 @@
         <v>161</v>
       </c>
       <c r="C24" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="E24" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="F24" s="39" t="s">
         <v>235</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="27.75" customHeight="1"/>
@@ -10721,37 +10715,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="46"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="46"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="47"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -10778,10 +10772,10 @@
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
       <c r="B6" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
@@ -10802,10 +10796,10 @@
     </row>
     <row r="7" spans="2:8" s="27" customFormat="1" ht="25.5">
       <c r="B7" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="D7" s="5">
         <v>4</v>
@@ -10826,10 +10820,10 @@
     </row>
     <row r="8" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
       <c r="B8" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D8" s="5">
         <v>3</v>
@@ -10850,10 +10844,10 @@
     </row>
     <row r="9" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
       <c r="B9" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="39" t="s">
         <v>243</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>244</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -10877,7 +10871,7 @@
         <v>171</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" s="5">
         <v>3</v>
@@ -10898,10 +10892,10 @@
     </row>
     <row r="11" spans="2:8" s="27" customFormat="1" ht="33.75" customHeight="1">
       <c r="B11" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -10925,7 +10919,7 @@
         <v>158</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D12" s="5">
         <v>2</v>
@@ -10949,7 +10943,7 @@
         <v>160</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -11038,14 +11032,14 @@
       <c r="B21" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="62" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11094,16 +11088,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="56"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="46"/>
+      <c r="C3" s="47"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -11138,136 +11132,147 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="66"/>
+      <c r="C9" s="65"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="51" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="52"/>
+    </row>
+    <row r="11" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B11" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="51"/>
-    </row>
-    <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="50" t="s">
+      <c r="C11" s="52"/>
+    </row>
+    <row r="12" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B12" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="C11" s="51"/>
-    </row>
-    <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="50" t="s">
+      <c r="C12" s="52"/>
+    </row>
+    <row r="13" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B13" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="C12" s="51"/>
-    </row>
-    <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="50" t="s">
+      <c r="C13" s="52"/>
+    </row>
+    <row r="14" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B14" s="51" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B14" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="51"/>
+      <c r="C14" s="52"/>
     </row>
     <row r="15" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B15" s="63"/>
-      <c r="C15" s="51"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="52"/>
     </row>
     <row r="16" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
     </row>
     <row r="17" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
     </row>
     <row r="18" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B18" s="63"/>
-      <c r="C18" s="51"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="52"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="72"/>
     </row>
     <row r="21" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="51" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="52"/>
+    </row>
+    <row r="22" spans="1:3" ht="25.5" customHeight="1">
+      <c r="B22" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="51"/>
-    </row>
-    <row r="22" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B22" s="50" t="s">
+      <c r="C22" s="52"/>
+    </row>
+    <row r="23" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B23" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="C22" s="51"/>
-    </row>
-    <row r="23" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="50" t="s">
+      <c r="C23" s="52"/>
+    </row>
+    <row r="24" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B24" s="67"/>
+      <c r="C24" s="52"/>
+    </row>
+    <row r="25" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+    </row>
+    <row r="26" spans="1:3" ht="25.5" customHeight="1">
+      <c r="B26" s="67"/>
+      <c r="C26" s="52"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1">
+      <c r="B28" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="70"/>
+    </row>
+    <row r="29" spans="1:3" ht="25.5" customHeight="1">
+      <c r="B29" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="C23" s="51"/>
-    </row>
-    <row r="24" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B24" s="63"/>
-      <c r="C24" s="51"/>
-    </row>
-    <row r="25" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B25" s="63"/>
-      <c r="C25" s="64"/>
-    </row>
-    <row r="26" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B26" s="63"/>
-      <c r="C26" s="51"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1">
-      <c r="B28" s="68" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="69"/>
-    </row>
-    <row r="29" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B29" s="50" t="s">
+      <c r="C29" s="52"/>
+    </row>
+    <row r="30" spans="1:3" ht="25.5" customHeight="1">
+      <c r="B30" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="C29" s="51"/>
-    </row>
-    <row r="30" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B30" s="50" t="s">
+      <c r="C30" s="52"/>
+    </row>
+    <row r="31" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B31" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="C30" s="51"/>
-    </row>
-    <row r="31" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="50" t="s">
-        <v>259</v>
-      </c>
-      <c r="C31" s="51"/>
+      <c r="C31" s="52"/>
     </row>
     <row r="32" spans="1:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B32" s="63"/>
-      <c r="C32" s="64"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68"/>
     </row>
     <row r="33" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="63"/>
-      <c r="C33" s="64"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68"/>
     </row>
     <row r="34" spans="2:3" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B34" s="63"/>
-      <c r="C34" s="64"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68"/>
     </row>
     <row r="35" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B35" s="63"/>
-      <c r="C35" s="51"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
@@ -11284,17 +11289,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11324,38 +11318,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="27.75" customHeight="1">
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
     </row>
     <row r="3" spans="2:17" ht="79.7" customHeight="1">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="46"/>
-      <c r="Q3" s="92" t="s">
-        <v>278</v>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="47"/>
+      <c r="Q3" s="43" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="25.5" customHeight="1">
@@ -11404,7 +11398,7 @@
         <v>58</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>175</v>
@@ -11437,10 +11431,10 @@
         <v>58</v>
       </c>
       <c r="D6" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>262</v>
       </c>
       <c r="F6" s="41">
         <v>46217</v>
@@ -11470,10 +11464,10 @@
         <v>59</v>
       </c>
       <c r="D7" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="F7" s="41">
         <v>46217</v>
@@ -11503,10 +11497,10 @@
         <v>59</v>
       </c>
       <c r="D8" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>266</v>
       </c>
       <c r="F8" s="41">
         <v>46217</v>
@@ -11519,10 +11513,10 @@
         <v>3</v>
       </c>
       <c r="I8" s="5">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -11536,7 +11530,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>175</v>
@@ -11569,7 +11563,7 @@
         <v>60</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>175</v>
@@ -11602,7 +11596,7 @@
         <v>60</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>175</v>
@@ -11635,7 +11629,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>175</v>
@@ -11668,7 +11662,7 @@
         <v>60</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>175</v>
@@ -11701,7 +11695,7 @@
         <v>174</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>175</v>
@@ -11720,7 +11714,7 @@
         <v>100</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -11734,7 +11728,7 @@
         <v>61</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>175</v>
@@ -11753,7 +11747,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>274</v>
+        <v>176</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -11767,10 +11761,10 @@
         <v>62</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F16" s="41">
         <v>46219</v>
@@ -11786,7 +11780,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -11800,10 +11794,10 @@
         <v>63</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F17" s="41">
         <v>46219</v>
@@ -11819,7 +11813,7 @@
         <v>100</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -11833,7 +11827,7 @@
         <v>64</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>175</v>
@@ -11849,10 +11843,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -11862,72 +11856,72 @@
       <c r="D19" s="27"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="75" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="87"/>
+      <c r="C20" s="76"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="89"/>
+      <c r="C21" s="78"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="91"/>
+      <c r="C22" s="80"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="84"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="77"/>
+      <c r="C24" s="86"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="79"/>
+      <c r="C25" s="88"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="81"/>
+      <c r="C26" s="90"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="82" t="s">
+      <c r="B27" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="83"/>
+      <c r="C27" s="92"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="73"/>
+      <c r="C28" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
@@ -11962,16 +11956,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="56"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="46"/>
+      <c r="C3" s="47"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
